--- a/バリデーション仕様書.xlsx
+++ b/バリデーション仕様書.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -954,8 +954,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="n"/>
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>ページ番号</t>
@@ -976,53 +976,30 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>取得件数</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>任意
-整数
-1以上100以下</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>取得件数は整数で指定してください
-取得件数は1以上の値で指定してください
-取得件数は100以下の値で指定してください</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>SearchIsbnRequest.php</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>GET /books/isbn/{isbn}
 ・Book\BookController@searchIsbn（画面・Ajax）</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>ISBN</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>必須
 数字13桁
 unique</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>ISBNを入力してください
 ISBNは13桁の数字で入力してください
@@ -1030,13 +1007,13 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>ReviewRequest.php</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>POST /books/{book}/reviews
 ・ReviewController@store（画面）
@@ -1044,19 +1021,19 @@
 ・ReviewController@update（画面）</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>評価</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>必須
 整数
 1〜5の間</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>評価を入力してください
 評価は1〜5の整数で入力してください
@@ -1064,34 +1041,34 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>コメント</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>必須
 最大255文字</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>コメントを入力してください
 コメントは255文字以内で入力してください</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>GenreRequest.php</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>POST /genres
 ・GenreController@store（画面）
@@ -1099,19 +1076,19 @@
 ・GenreController@update（画面）</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>ジャンル名</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>必須
 最大20文字
 unique</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>ジャンル名を入力してください
 ジャンル名は20文字以内で入力してください
@@ -1119,13 +1096,13 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>ReadingPlanRequest.php</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>POST /reading-plans
 ・ReadingPlanController@store（画面）
@@ -1133,19 +1110,19 @@
 ・ReadingPlanController@update（画面）</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>書籍ID（新規作成時のみ）</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>必須
 整数
 存在確認</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>書籍を選択してください
 書籍の指定が正しくありません
@@ -1153,22 +1130,22 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>期日（新規作成・更新共通）</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>必須
 日付形式
 今日以降の日付設定</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>期日を入力してください
 正しい日付を入力してください
@@ -1176,20 +1153,22 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
+    <row r="26"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B16:B19"/>
-    <mergeCell ref="B2:B5"/>
     <mergeCell ref="A9:A15"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B9:B15"/>
-    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
     <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="B16:B18"/>
     <mergeCell ref="B6:B8"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/バリデーション仕様書.xlsx
+++ b/バリデーション仕様書.xlsx
@@ -1153,21 +1153,19 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="A6:A8"/>
     <mergeCell ref="A9:A15"/>
+    <mergeCell ref="A16:A18"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B9:B15"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="B20:B21"/>
-    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B16:B18"/>
     <mergeCell ref="B2:B5"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="B16:B18"/>
     <mergeCell ref="B6:B8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1180,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1206,8 +1204,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="n">
-        <v>1</v>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
@@ -1221,8 +1221,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="n">
-        <v>2</v>
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
@@ -1236,8 +1238,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="n">
-        <v>3</v>
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B4" s="10" t="n"/>
       <c r="C4" s="9" t="inlineStr">
@@ -1247,8 +1251,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n">
-        <v>4</v>
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
@@ -1262,8 +1268,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n">
-        <v>5</v>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B6" s="11" t="n"/>
       <c r="C6" s="9" t="inlineStr">
@@ -1273,8 +1281,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n">
-        <v>6</v>
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B7" s="10" t="n"/>
       <c r="C7" s="9" t="inlineStr">
@@ -1284,8 +1294,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n">
-        <v>7</v>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
@@ -1299,8 +1311,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n">
-        <v>8</v>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="9" t="inlineStr">
@@ -1310,8 +1324,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n">
-        <v>9</v>
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
@@ -1325,37 +1341,72 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n">
-        <v>10</v>
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
+          <t>ReviewRequest.php</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>authorize() で ReviewPolicy を呼び出しているため、権限の判定は入力チェック（rules）より先に行われる。投稿（POST）はその書籍にまだレビューを投稿していない場合のみ、更新（PUT）はレビューの投稿者本人のみ許可され、それ以外は入力内容にかかわらず 403 を返す（422 にはならない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
           <t>ReadingPlanRequest.php</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>編集画面では期日のみ変更できるため、書籍ID（book_id）のバリデーションは新規作成時のみ行う（rules() 内で $this-&gt;route('readingPlan') の有無により分岐）。</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>authorize() で ReadingPlanPolicy を呼び出しているため、権限の判定は入力チェック（rules）より先に行われる。作成（POST）は選択した書籍に自分の「進行中」の計画がない場合のみ、更新（PUT）は計画の作成者本人かつ更新可能な状態の場合のみ許可され、それ以外は入力内容にかかわらず 403 を返す（422 にはならない）。書籍が特定できない場合（未選択・存在しないIDなど）は許可し、入力チェックでエラーにする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>BookIndexRequest.php</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>API 専用の FormRequest。画面の書籍一覧（Book\BookController@index）には対応する FormRequest はなく、パラメータを直接受け取っている。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="B5:B7"/>

--- a/バリデーション仕様書.xlsx
+++ b/バリデーション仕様書.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -954,8 +954,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="n"/>
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>ページ番号</t>
@@ -976,30 +976,55 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1ページの件数</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>任意
+整数
+1以上
+100以下
+（未指定の場合は20件）</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1ページの件数は整数で指定してください
+1ページの件数は1以上の値で指定してください
+1ページの件数は100以下の値で指定してください</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>SearchIsbnRequest.php</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>GET /books/isbn/{isbn}
 ・Book\BookController@searchIsbn（画面・Ajax）</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>ISBN</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>必須
 数字13桁
 unique</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>ISBNを入力してください
 ISBNは13桁の数字で入力してください
@@ -1007,13 +1032,13 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>ReviewRequest.php</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>POST /books/{book}/reviews
 ・ReviewController@store（画面）
@@ -1021,19 +1046,19 @@
 ・ReviewController@update（画面）</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>評価</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>必須
 整数
 1〜5の間</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>評価を入力してください
 評価は1〜5の整数で入力してください
@@ -1041,34 +1066,34 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>コメント</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>必須
 最大255文字</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>コメントを入力してください
 コメントは255文字以内で入力してください</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>GenreRequest.php</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>POST /genres
 ・GenreController@store（画面）
@@ -1076,19 +1101,19 @@
 ・GenreController@update（画面）</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>ジャンル名</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>必須
 最大20文字
 unique</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>ジャンル名を入力してください
 ジャンル名は20文字以内で入力してください
@@ -1096,13 +1121,13 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>ReadingPlanRequest.php</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>POST /reading-plans
 ・ReadingPlanController@store（画面）
@@ -1110,19 +1135,19 @@
 ・ReadingPlanController@update（画面）</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>書籍ID（新規作成時のみ）</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>必須
 整数
 存在確認</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>書籍を選択してください
 書籍の指定が正しくありません
@@ -1130,22 +1155,22 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="n"/>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>期日（新規作成・更新共通）</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>必須
 日付形式
 今日以降の日付設定</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>期日を入力してください
 正しい日付を入力してください
@@ -1155,18 +1180,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B21:B22"/>
     <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B16:B19"/>
+    <mergeCell ref="B2:B5"/>
     <mergeCell ref="A9:A15"/>
-    <mergeCell ref="A16:A18"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B9:B15"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="B24:B25"/>
     <mergeCell ref="B6:B8"/>
+    <mergeCell ref="A21:A22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
